--- a/DADOS.xlsx
+++ b/DADOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ESTACA\BI METAS E ACOMPANHAMENTO\VISÃO PARA A ÁREA 2026 - 2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C21A9EB-2814-433F-99D9-18EE94A5DD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9737D2-FA0A-442F-9C67-9940982900DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF28A7F4-3A70-4350-B721-E9BE457B7268}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12075" windowHeight="15585" xr2:uid="{AF28A7F4-3A70-4350-B721-E9BE457B7268}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -886,8 +886,12 @@
       <c r="C2" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="61"/>
-      <c r="E2" s="62"/>
+      <c r="D2" s="61">
+        <v>100</v>
+      </c>
+      <c r="E2" s="62">
+        <v>60</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="60">
@@ -899,8 +903,12 @@
       <c r="C3" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62"/>
+      <c r="D3" s="61">
+        <v>100</v>
+      </c>
+      <c r="E3" s="62">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="60">
@@ -912,8 +920,12 @@
       <c r="C4" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="61"/>
-      <c r="E4" s="62"/>
+      <c r="D4" s="61">
+        <v>5</v>
+      </c>
+      <c r="E4" s="62">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -925,8 +937,12 @@
       <c r="C5" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="61"/>
-      <c r="E5" s="62"/>
+      <c r="D5" s="61">
+        <v>50</v>
+      </c>
+      <c r="E5" s="62">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="60">
@@ -938,8 +954,12 @@
       <c r="C6" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="62"/>
+      <c r="D6" s="61">
+        <v>12</v>
+      </c>
+      <c r="E6" s="62">
+        <v>7</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="60">
@@ -951,8 +971,12 @@
       <c r="C7" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="61"/>
-      <c r="E7" s="62"/>
+      <c r="D7" s="61">
+        <v>4</v>
+      </c>
+      <c r="E7" s="62">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="60">
@@ -964,8 +988,12 @@
       <c r="C8" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="62"/>
+      <c r="D8" s="61">
+        <v>60</v>
+      </c>
+      <c r="E8" s="62">
+        <v>45</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="87">
@@ -977,8 +1005,12 @@
       <c r="C9" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="88"/>
-      <c r="E9" s="89"/>
+      <c r="D9" s="88">
+        <v>25</v>
+      </c>
+      <c r="E9" s="89">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="87">
@@ -1016,8 +1048,12 @@
       <c r="C12" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="D12" s="25">
+        <v>70</v>
+      </c>
+      <c r="E12" s="26">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="27">
@@ -1029,8 +1065,12 @@
       <c r="C13" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="D13" s="28">
+        <v>70</v>
+      </c>
+      <c r="E13" s="29">
+        <v>46</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="27">
@@ -1042,8 +1082,12 @@
       <c r="C14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
+      <c r="D14" s="28">
+        <v>50</v>
+      </c>
+      <c r="E14" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="27">
@@ -1055,8 +1099,12 @@
       <c r="C15" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="29"/>
+      <c r="D15" s="28">
+        <v>20</v>
+      </c>
+      <c r="E15" s="29">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="27">
@@ -1068,8 +1116,12 @@
       <c r="C16" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="29"/>
+      <c r="D16" s="28">
+        <v>24</v>
+      </c>
+      <c r="E16" s="29">
+        <v>9</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="27">
@@ -1081,8 +1133,12 @@
       <c r="C17" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="29"/>
+      <c r="D17" s="28">
+        <v>2</v>
+      </c>
+      <c r="E17" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="27">
@@ -1094,8 +1150,12 @@
       <c r="C18" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
+      <c r="D18" s="28">
+        <v>20</v>
+      </c>
+      <c r="E18" s="29">
+        <v>19</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="27">
@@ -1107,8 +1167,12 @@
       <c r="C19" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="91"/>
-      <c r="E19" s="92"/>
+      <c r="D19" s="91">
+        <v>20</v>
+      </c>
+      <c r="E19" s="92">
+        <v>9</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="90">
@@ -1146,8 +1210,12 @@
       <c r="C22" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
+      <c r="D22" s="34">
+        <v>105</v>
+      </c>
+      <c r="E22" s="35">
+        <v>61</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="36">
@@ -1159,8 +1227,12 @@
       <c r="C23" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
+      <c r="D23" s="37">
+        <v>97</v>
+      </c>
+      <c r="E23" s="38">
+        <v>105</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
@@ -1172,8 +1244,12 @@
       <c r="C24" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="38"/>
+      <c r="D24" s="37">
+        <v>15</v>
+      </c>
+      <c r="E24" s="38">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="36">
@@ -1185,8 +1261,12 @@
       <c r="C25" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="38"/>
+      <c r="D25" s="37">
+        <v>40</v>
+      </c>
+      <c r="E25" s="38">
+        <v>9</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
@@ -1198,8 +1278,12 @@
       <c r="C26" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="38"/>
+      <c r="D26" s="37">
+        <v>24</v>
+      </c>
+      <c r="E26" s="38">
+        <v>12</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="36">
@@ -1211,8 +1295,12 @@
       <c r="C27" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="37"/>
-      <c r="E27" s="38"/>
+      <c r="D27" s="37">
+        <v>6</v>
+      </c>
+      <c r="E27" s="38">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="36">
@@ -1224,8 +1312,12 @@
       <c r="C28" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="37"/>
-      <c r="E28" s="38"/>
+      <c r="D28" s="37">
+        <v>45</v>
+      </c>
+      <c r="E28" s="38">
+        <v>33</v>
+      </c>
     </row>
     <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
@@ -1237,8 +1329,12 @@
       <c r="C29" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="40"/>
-      <c r="E29" s="41"/>
+      <c r="D29" s="40">
+        <v>35</v>
+      </c>
+      <c r="E29" s="41">
+        <v>14</v>
+      </c>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A30" s="42">
@@ -1250,8 +1346,12 @@
       <c r="C30" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="43"/>
-      <c r="E30" s="44"/>
+      <c r="D30" s="43">
+        <v>100</v>
+      </c>
+      <c r="E30" s="44">
+        <v>63</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="45">
@@ -1263,8 +1363,12 @@
       <c r="C31" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="46"/>
-      <c r="E31" s="47"/>
+      <c r="D31" s="46">
+        <v>100</v>
+      </c>
+      <c r="E31" s="47">
+        <v>91</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="45">
@@ -1276,8 +1380,12 @@
       <c r="C32" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="46"/>
-      <c r="E32" s="47"/>
+      <c r="D32" s="46">
+        <v>15</v>
+      </c>
+      <c r="E32" s="47">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="45">
@@ -1289,8 +1397,12 @@
       <c r="C33" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="46"/>
-      <c r="E33" s="47"/>
+      <c r="D33" s="46">
+        <v>40</v>
+      </c>
+      <c r="E33" s="47">
+        <v>21</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="45">
@@ -1302,8 +1414,12 @@
       <c r="C34" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="D34" s="46"/>
-      <c r="E34" s="47"/>
+      <c r="D34" s="46">
+        <v>12</v>
+      </c>
+      <c r="E34" s="47">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="45">
@@ -1315,8 +1431,12 @@
       <c r="C35" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="46"/>
-      <c r="E35" s="47"/>
+      <c r="D35" s="46">
+        <v>4</v>
+      </c>
+      <c r="E35" s="47">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="45">
@@ -1328,8 +1448,12 @@
       <c r="C36" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="46"/>
-      <c r="E36" s="47"/>
+      <c r="D36" s="46">
+        <v>50</v>
+      </c>
+      <c r="E36" s="47">
+        <v>45</v>
+      </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="48">
@@ -1341,8 +1465,12 @@
       <c r="C37" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="49"/>
-      <c r="E37" s="50"/>
+      <c r="D37" s="49">
+        <v>20</v>
+      </c>
+      <c r="E37" s="50">
+        <v>9</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A38" s="51">
@@ -1358,7 +1486,7 @@
         <v>120</v>
       </c>
       <c r="E38" s="53">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1375,7 +1503,7 @@
         <v>140</v>
       </c>
       <c r="E39" s="56">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1409,7 +1537,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="56">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1457,10 +1585,10 @@
         <v>7</v>
       </c>
       <c r="D44" s="55">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E44" s="56">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1477,7 +1605,7 @@
         <v>35</v>
       </c>
       <c r="E45" s="59">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -1490,8 +1618,12 @@
       <c r="C46" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="67"/>
-      <c r="E46" s="68"/>
+      <c r="D46" s="67">
+        <v>80</v>
+      </c>
+      <c r="E46" s="68">
+        <v>33</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="69">
@@ -1503,8 +1635,12 @@
       <c r="C47" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="70"/>
-      <c r="E47" s="71"/>
+      <c r="D47" s="70">
+        <v>30</v>
+      </c>
+      <c r="E47" s="71">
+        <v>45</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="69">
@@ -1516,8 +1652,12 @@
       <c r="C48" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="70"/>
-      <c r="E48" s="71"/>
+      <c r="D48" s="70">
+        <v>10</v>
+      </c>
+      <c r="E48" s="71">
+        <v>0</v>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="69">
@@ -1529,8 +1669,12 @@
       <c r="C49" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="70"/>
-      <c r="E49" s="71"/>
+      <c r="D49" s="70">
+        <v>40</v>
+      </c>
+      <c r="E49" s="71">
+        <v>5</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="69">
@@ -1542,8 +1686,12 @@
       <c r="C50" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="70"/>
-      <c r="E50" s="71"/>
+      <c r="D50" s="70">
+        <v>30</v>
+      </c>
+      <c r="E50" s="71">
+        <v>6</v>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="69">
@@ -1555,8 +1703,12 @@
       <c r="C51" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="D51" s="70"/>
-      <c r="E51" s="71"/>
+      <c r="D51" s="70">
+        <v>5</v>
+      </c>
+      <c r="E51" s="71">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="69">
@@ -1568,8 +1720,12 @@
       <c r="C52" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="D52" s="70"/>
-      <c r="E52" s="71"/>
+      <c r="D52" s="70">
+        <v>15</v>
+      </c>
+      <c r="E52" s="71">
+        <v>14</v>
+      </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="72">
@@ -1581,8 +1737,12 @@
       <c r="C53" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="D53" s="73"/>
-      <c r="E53" s="74"/>
+      <c r="D53" s="73">
+        <v>30</v>
+      </c>
+      <c r="E53" s="74">
+        <v>7</v>
+      </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="75">
@@ -1594,8 +1754,12 @@
       <c r="C54" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="D54" s="76"/>
-      <c r="E54" s="77"/>
+      <c r="D54" s="76">
+        <v>100</v>
+      </c>
+      <c r="E54" s="77">
+        <v>67</v>
+      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="78">
@@ -1607,8 +1771,12 @@
       <c r="C55" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="79"/>
-      <c r="E55" s="80"/>
+      <c r="D55" s="79">
+        <v>115</v>
+      </c>
+      <c r="E55" s="80">
+        <v>96</v>
+      </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="78">
@@ -1620,8 +1788,12 @@
       <c r="C56" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="D56" s="79"/>
-      <c r="E56" s="80"/>
+      <c r="D56" s="79">
+        <v>10</v>
+      </c>
+      <c r="E56" s="80">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="78">
@@ -1633,8 +1805,12 @@
       <c r="C57" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="79"/>
-      <c r="E57" s="80"/>
+      <c r="D57" s="79">
+        <v>40</v>
+      </c>
+      <c r="E57" s="80">
+        <v>9</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="78">
@@ -1646,8 +1822,12 @@
       <c r="C58" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="D58" s="79"/>
-      <c r="E58" s="80"/>
+      <c r="D58" s="79">
+        <v>12</v>
+      </c>
+      <c r="E58" s="80">
+        <v>20</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="78">
@@ -1659,8 +1839,12 @@
       <c r="C59" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="79"/>
-      <c r="E59" s="80"/>
+      <c r="D59" s="79">
+        <v>4</v>
+      </c>
+      <c r="E59" s="80">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="78">
@@ -1672,8 +1856,12 @@
       <c r="C60" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="79"/>
-      <c r="E60" s="80"/>
+      <c r="D60" s="79">
+        <v>50</v>
+      </c>
+      <c r="E60" s="80">
+        <v>38</v>
+      </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="81">
@@ -1685,8 +1873,12 @@
       <c r="C61" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="82"/>
-      <c r="E61" s="83"/>
+      <c r="D61" s="82">
+        <v>25</v>
+      </c>
+      <c r="E61" s="83">
+        <v>12</v>
+      </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
@@ -1700,11 +1892,11 @@
       </c>
       <c r="D62" s="7">
         <f t="shared" ref="D62:E68" si="0">SUM(D54,D46,D38,D30,D22,D12,D2)</f>
-        <v>120</v>
+        <v>675</v>
       </c>
       <c r="E62" s="8">
         <f t="shared" si="0"/>
-        <v>79</v>
+        <v>368</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1719,11 +1911,11 @@
       </c>
       <c r="D63" s="10">
         <f t="shared" si="0"/>
-        <v>140</v>
+        <v>652</v>
       </c>
       <c r="E63" s="11">
         <f t="shared" si="0"/>
-        <v>113</v>
+        <v>583</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1738,7 +1930,7 @@
       </c>
       <c r="D64" s="10">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="E64" s="11">
         <f t="shared" si="0"/>
@@ -1757,11 +1949,11 @@
       </c>
       <c r="D65" s="10">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="E65" s="11">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -1776,11 +1968,11 @@
       </c>
       <c r="D66" s="10">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E66" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -1795,11 +1987,11 @@
       </c>
       <c r="D67" s="10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E67" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -1814,11 +2006,11 @@
       </c>
       <c r="D68" s="10">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>296</v>
       </c>
       <c r="E68" s="11">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>247</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1833,11 +2025,11 @@
       </c>
       <c r="D69" s="13">
         <f>SUM(D61,D53,D45,D37,D29,D21,D11)</f>
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="E69" s="14">
         <f>SUM(E61,E53,E45,E37,E29,E21,E11)</f>
-        <v>21</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">

--- a/DADOS.xlsx
+++ b/DADOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ESTACA\BI METAS E ACOMPANHAMENTO\VISÃO PARA A ÁREA 2026 - 2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9737D2-FA0A-442F-9C67-9940982900DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D14D078-AD15-40A2-9E81-12BEC90A4746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="12075" windowHeight="15585" xr2:uid="{AF28A7F4-3A70-4350-B721-E9BE457B7268}"/>
+    <workbookView xWindow="3000" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{AF28A7F4-3A70-4350-B721-E9BE457B7268}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="25">
   <si>
     <t>TOPICO</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Missionários Servindo do Brasil</t>
+  </si>
+  <si>
+    <t>FALTA</t>
   </si>
 </sst>
 </file>
@@ -190,7 +193,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -411,11 +414,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -435,9 +449,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -511,10 +522,36 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -849,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F96C0220-435A-457F-9268-B5B862FCBE35}">
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -859,7 +896,7 @@
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>2</v>
       </c>
@@ -872,1168 +909,1431 @@
       <c r="D1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="90" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="60">
-        <v>2026</v>
-      </c>
-      <c r="B2" s="61" t="s">
+      <c r="F1" s="113" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="59">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="61">
+      <c r="D2" s="60">
         <v>100</v>
       </c>
-      <c r="E2" s="62">
+      <c r="E2" s="91">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="60">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="61" t="s">
+      <c r="F2" s="61">
+        <f>D2-E2</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="59">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="61">
+      <c r="D3" s="60">
         <v>100</v>
       </c>
-      <c r="E3" s="62">
+      <c r="E3" s="91">
         <v>93</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="60">
-        <v>2026</v>
-      </c>
-      <c r="B4" s="61" t="s">
+      <c r="F3" s="61">
+        <f t="shared" ref="F3:F9" si="0">D3-E3</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="59">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="60">
         <v>5</v>
       </c>
-      <c r="E4" s="62">
+      <c r="E4" s="91">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="60">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="61" t="s">
+      <c r="F4" s="61">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="59">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="61">
+      <c r="D5" s="60">
         <v>50</v>
       </c>
-      <c r="E5" s="62">
+      <c r="E5" s="91">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="60">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="61" t="s">
+      <c r="F5" s="61">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="59">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="61">
+      <c r="D6" s="60">
         <v>12</v>
       </c>
-      <c r="E6" s="62">
+      <c r="E6" s="91">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="60">
-        <v>2026</v>
-      </c>
-      <c r="B7" s="61" t="s">
+      <c r="F6" s="61">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="59">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="60">
         <v>4</v>
       </c>
-      <c r="E7" s="62">
+      <c r="E7" s="91">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="60">
-        <v>2026</v>
-      </c>
-      <c r="B8" s="61" t="s">
+      <c r="F7" s="61">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="59">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="60">
         <v>60</v>
       </c>
-      <c r="E8" s="62">
+      <c r="E8" s="91">
         <v>45</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="87">
-        <v>2026</v>
-      </c>
-      <c r="B9" s="61" t="s">
+      <c r="F8" s="61">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="86">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="88">
+      <c r="D9" s="87">
         <v>25</v>
       </c>
-      <c r="E9" s="89">
+      <c r="E9" s="92">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="87">
-        <v>2026</v>
-      </c>
-      <c r="B10" s="61" t="s">
+      <c r="F9" s="61">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="86">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="88"/>
-      <c r="E10" s="89"/>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="63">
-        <v>2026</v>
-      </c>
-      <c r="B11" s="61" t="s">
+      <c r="D10" s="87"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="61"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="62">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C11" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="65"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24">
-        <v>2026</v>
-      </c>
-      <c r="B12" s="25" t="s">
+      <c r="D11" s="63"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="64"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="23">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="24">
         <v>70</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="94">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="27">
-        <v>2026</v>
-      </c>
-      <c r="B13" s="28" t="s">
+      <c r="F12" s="25">
+        <f>D12-E12</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="26">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="27">
         <v>70</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="95">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
-        <v>2026</v>
-      </c>
-      <c r="B14" s="28" t="s">
+      <c r="F13" s="28">
+        <f t="shared" ref="F13:F19" si="1">D13-E13</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="26">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="27">
         <v>50</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="95">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="27">
-        <v>2026</v>
-      </c>
-      <c r="B15" s="28" t="s">
+      <c r="F14" s="28">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="26">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="27">
         <v>20</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="95">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="27">
-        <v>2026</v>
-      </c>
-      <c r="B16" s="28" t="s">
+      <c r="F15" s="28">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="26">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="27">
         <v>24</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="95">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="27">
-        <v>2026</v>
-      </c>
-      <c r="B17" s="28" t="s">
+      <c r="F16" s="28">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="26">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <v>2</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="95">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="27">
-        <v>2026</v>
-      </c>
-      <c r="B18" s="28" t="s">
+      <c r="F17" s="28">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="26">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="27">
         <v>20</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="95">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="27">
-        <v>2026</v>
-      </c>
-      <c r="B19" s="28" t="s">
+      <c r="F18" s="28">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="26">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="91">
+      <c r="D19" s="89">
         <v>20</v>
       </c>
-      <c r="E19" s="92">
+      <c r="E19" s="96">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="90">
-        <v>2026</v>
-      </c>
-      <c r="B20" s="28" t="s">
+      <c r="F19" s="28">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="88">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="91" t="s">
+      <c r="C20" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="91"/>
-      <c r="E20" s="92"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="30">
-        <v>2026</v>
-      </c>
-      <c r="B21" s="28" t="s">
+      <c r="D20" s="89"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="28"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="31"/>
-      <c r="E21" s="32"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="33">
-        <v>2026</v>
-      </c>
-      <c r="B22" s="34" t="s">
+      <c r="D21" s="30"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="31"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="32">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="33">
         <v>105</v>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="98">
         <v>61</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="36">
-        <v>2026</v>
-      </c>
-      <c r="B23" s="37" t="s">
+      <c r="F22" s="34">
+        <f>D22-E22</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="35">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="37">
+      <c r="D23" s="36">
         <v>97</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E23" s="99">
         <v>105</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="36">
-        <v>2026</v>
-      </c>
-      <c r="B24" s="37" t="s">
+      <c r="F23" s="37">
+        <f t="shared" ref="F23:F69" si="2">D23-E23</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="35">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="37">
+      <c r="D24" s="36">
         <v>15</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="99">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="36">
-        <v>2026</v>
-      </c>
-      <c r="B25" s="37" t="s">
+      <c r="F24" s="37">
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="C25" s="37" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="35">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="36">
         <v>40</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25" s="99">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="36">
-        <v>2026</v>
-      </c>
-      <c r="B26" s="37" t="s">
+      <c r="F25" s="37">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="35">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="37">
+      <c r="D26" s="36">
         <v>24</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="99">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="36">
-        <v>2026</v>
-      </c>
-      <c r="B27" s="37" t="s">
+      <c r="F26" s="37">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="35">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C27" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="37">
+      <c r="D27" s="36">
         <v>6</v>
       </c>
-      <c r="E27" s="38">
+      <c r="E27" s="99">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="36">
-        <v>2026</v>
-      </c>
-      <c r="B28" s="37" t="s">
+      <c r="F27" s="37">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="35">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="37">
+      <c r="D28" s="36">
         <v>45</v>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="99">
         <v>33</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="39">
-        <v>2026</v>
-      </c>
-      <c r="B29" s="37" t="s">
+      <c r="F28" s="37">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="38">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="39">
         <v>35</v>
       </c>
-      <c r="E29" s="41">
+      <c r="E29" s="100">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="42">
-        <v>2026</v>
-      </c>
-      <c r="B30" s="43" t="s">
+      <c r="F29" s="40">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="41">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="43" t="s">
+      <c r="C30" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="42">
         <v>100</v>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="101">
         <v>63</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="45">
-        <v>2026</v>
-      </c>
-      <c r="B31" s="46" t="s">
+      <c r="F30" s="43">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="46">
+      <c r="D31" s="45">
         <v>100</v>
       </c>
-      <c r="E31" s="47">
+      <c r="E31" s="102">
         <v>91</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="45">
-        <v>2026</v>
-      </c>
-      <c r="B32" s="46" t="s">
+      <c r="F31" s="46">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="46">
+      <c r="D32" s="45">
         <v>15</v>
       </c>
-      <c r="E32" s="47">
+      <c r="E32" s="102">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="45">
-        <v>2026</v>
-      </c>
-      <c r="B33" s="46" t="s">
+      <c r="F32" s="46">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="46">
+      <c r="D33" s="45">
         <v>40</v>
       </c>
-      <c r="E33" s="47">
+      <c r="E33" s="102">
         <v>21</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="45">
-        <v>2026</v>
-      </c>
-      <c r="B34" s="46" t="s">
+      <c r="F33" s="46">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="46" t="s">
+      <c r="C34" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="D34" s="46">
+      <c r="D34" s="45">
         <v>12</v>
       </c>
-      <c r="E34" s="47">
+      <c r="E34" s="102">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="45">
-        <v>2026</v>
-      </c>
-      <c r="B35" s="46" t="s">
+      <c r="F34" s="46">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="46" t="s">
+      <c r="C35" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="46">
+      <c r="D35" s="45">
         <v>4</v>
       </c>
-      <c r="E35" s="47">
+      <c r="E35" s="102">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="45">
-        <v>2026</v>
-      </c>
-      <c r="B36" s="46" t="s">
+      <c r="F35" s="46">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="44">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="46" t="s">
+      <c r="C36" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="46">
+      <c r="D36" s="45">
         <v>50</v>
       </c>
-      <c r="E36" s="47">
+      <c r="E36" s="102">
         <v>45</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48">
-        <v>2026</v>
-      </c>
-      <c r="B37" s="46" t="s">
+      <c r="F36" s="46">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="47">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="C37" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="49">
+      <c r="D37" s="48">
         <v>20</v>
       </c>
-      <c r="E37" s="50">
+      <c r="E37" s="103">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="51">
-        <v>2026</v>
-      </c>
-      <c r="B38" s="52" t="s">
+      <c r="F37" s="49">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="50">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="52" t="s">
+      <c r="C38" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="52">
+      <c r="D38" s="51">
         <v>120</v>
       </c>
-      <c r="E38" s="53">
+      <c r="E38" s="104">
         <v>84</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="54">
-        <v>2026</v>
-      </c>
-      <c r="B39" s="55" t="s">
+      <c r="F38" s="52">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="53">
+        <v>2026</v>
+      </c>
+      <c r="B39" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="55" t="s">
+      <c r="C39" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="55">
+      <c r="D39" s="54">
         <v>140</v>
       </c>
-      <c r="E39" s="56">
+      <c r="E39" s="105">
         <v>107</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="54">
-        <v>2026</v>
-      </c>
-      <c r="B40" s="55" t="s">
+      <c r="F39" s="55">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="53">
+        <v>2026</v>
+      </c>
+      <c r="B40" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="55" t="s">
+      <c r="C40" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="55">
+      <c r="D40" s="54">
         <v>30</v>
       </c>
-      <c r="E40" s="56">
+      <c r="E40" s="105">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="54">
-        <v>2026</v>
-      </c>
-      <c r="B41" s="55" t="s">
+      <c r="F40" s="55">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="53">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="55" t="s">
+      <c r="C41" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="55">
+      <c r="D41" s="54">
         <v>27</v>
       </c>
-      <c r="E41" s="56">
+      <c r="E41" s="105">
         <v>9</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="54">
-        <v>2026</v>
-      </c>
-      <c r="B42" s="55" t="s">
+      <c r="F41" s="55">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="53">
+        <v>2026</v>
+      </c>
+      <c r="B42" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="55" t="s">
+      <c r="C42" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="55">
+      <c r="D42" s="54">
         <v>20</v>
       </c>
-      <c r="E42" s="56">
+      <c r="E42" s="105">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="54">
-        <v>2026</v>
-      </c>
-      <c r="B43" s="55" t="s">
+      <c r="F42" s="55">
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="C43" s="55" t="s">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="53">
+        <v>2026</v>
+      </c>
+      <c r="B43" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="55">
+      <c r="D43" s="54">
         <v>3</v>
       </c>
-      <c r="E43" s="56">
+      <c r="E43" s="105">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="54">
-        <v>2026</v>
-      </c>
-      <c r="B44" s="55" t="s">
+      <c r="F43" s="55">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="53">
+        <v>2026</v>
+      </c>
+      <c r="B44" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C44" s="55" t="s">
+      <c r="C44" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="D44" s="55">
+      <c r="D44" s="54">
         <v>56</v>
       </c>
-      <c r="E44" s="56">
+      <c r="E44" s="105">
         <v>53</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="57">
-        <v>2026</v>
-      </c>
-      <c r="B45" s="55" t="s">
+      <c r="F44" s="55">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="56">
+        <v>2026</v>
+      </c>
+      <c r="B45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="58" t="s">
+      <c r="C45" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="58">
+      <c r="D45" s="57">
         <v>35</v>
       </c>
-      <c r="E45" s="59">
+      <c r="E45" s="106">
         <v>19</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="66">
-        <v>2026</v>
-      </c>
-      <c r="B46" s="67" t="s">
+      <c r="F45" s="58">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="65">
+        <v>2026</v>
+      </c>
+      <c r="B46" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="67">
+      <c r="D46" s="66">
         <v>80</v>
       </c>
-      <c r="E46" s="68">
+      <c r="E46" s="107">
         <v>33</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="69">
-        <v>2026</v>
-      </c>
-      <c r="B47" s="70" t="s">
+      <c r="F46" s="67">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="68">
+        <v>2026</v>
+      </c>
+      <c r="B47" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C47" s="70" t="s">
+      <c r="C47" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="70">
+      <c r="D47" s="69">
         <v>30</v>
       </c>
-      <c r="E47" s="71">
+      <c r="E47" s="108">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="69">
-        <v>2026</v>
-      </c>
-      <c r="B48" s="70" t="s">
+      <c r="F47" s="70">
+        <f t="shared" si="2"/>
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="68">
+        <v>2026</v>
+      </c>
+      <c r="B48" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="70" t="s">
+      <c r="C48" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="70">
+      <c r="D48" s="69">
         <v>10</v>
       </c>
-      <c r="E48" s="71">
+      <c r="E48" s="108">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="69">
-        <v>2026</v>
-      </c>
-      <c r="B49" s="70" t="s">
+      <c r="F48" s="70">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="68">
+        <v>2026</v>
+      </c>
+      <c r="B49" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C49" s="70" t="s">
+      <c r="C49" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="70">
+      <c r="D49" s="69">
         <v>40</v>
       </c>
-      <c r="E49" s="71">
+      <c r="E49" s="108">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="69">
-        <v>2026</v>
-      </c>
-      <c r="B50" s="70" t="s">
+      <c r="F49" s="70">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="68">
+        <v>2026</v>
+      </c>
+      <c r="B50" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C50" s="70" t="s">
+      <c r="C50" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="70">
+      <c r="D50" s="69">
         <v>30</v>
       </c>
-      <c r="E50" s="71">
+      <c r="E50" s="108">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="69">
-        <v>2026</v>
-      </c>
-      <c r="B51" s="70" t="s">
+      <c r="F50" s="70">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="68">
+        <v>2026</v>
+      </c>
+      <c r="B51" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="70" t="s">
+      <c r="C51" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D51" s="70">
+      <c r="D51" s="69">
         <v>5</v>
       </c>
-      <c r="E51" s="71">
+      <c r="E51" s="108">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="69">
-        <v>2026</v>
-      </c>
-      <c r="B52" s="70" t="s">
+      <c r="F51" s="70">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="68">
+        <v>2026</v>
+      </c>
+      <c r="B52" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="70" t="s">
+      <c r="C52" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="D52" s="70">
+      <c r="D52" s="69">
         <v>15</v>
       </c>
-      <c r="E52" s="71">
+      <c r="E52" s="108">
         <v>14</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="72">
-        <v>2026</v>
-      </c>
-      <c r="B53" s="73" t="s">
+      <c r="F52" s="70">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="71">
+        <v>2026</v>
+      </c>
+      <c r="B53" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="73" t="s">
+      <c r="C53" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="D53" s="73">
+      <c r="D53" s="72">
         <v>30</v>
       </c>
-      <c r="E53" s="74">
+      <c r="E53" s="109">
         <v>7</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="75">
-        <v>2026</v>
-      </c>
-      <c r="B54" s="76" t="s">
+      <c r="F53" s="73">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="74">
+        <v>2026</v>
+      </c>
+      <c r="B54" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="76" t="s">
+      <c r="C54" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="D54" s="76">
+      <c r="D54" s="75">
         <v>100</v>
       </c>
-      <c r="E54" s="77">
+      <c r="E54" s="110">
         <v>67</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="78">
-        <v>2026</v>
-      </c>
-      <c r="B55" s="79" t="s">
+      <c r="F54" s="76">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="77">
+        <v>2026</v>
+      </c>
+      <c r="B55" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C55" s="79" t="s">
+      <c r="C55" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="79">
+      <c r="D55" s="78">
         <v>115</v>
       </c>
-      <c r="E55" s="80">
+      <c r="E55" s="111">
         <v>96</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="78">
-        <v>2026</v>
-      </c>
-      <c r="B56" s="79" t="s">
+      <c r="F55" s="79">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="77">
+        <v>2026</v>
+      </c>
+      <c r="B56" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="79" t="s">
+      <c r="C56" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="D56" s="79">
+      <c r="D56" s="78">
         <v>10</v>
       </c>
-      <c r="E56" s="80">
+      <c r="E56" s="111">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="78">
-        <v>2026</v>
-      </c>
-      <c r="B57" s="79" t="s">
+      <c r="F56" s="79">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="77">
+        <v>2026</v>
+      </c>
+      <c r="B57" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="79" t="s">
+      <c r="C57" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="79">
+      <c r="D57" s="78">
         <v>40</v>
       </c>
-      <c r="E57" s="80">
+      <c r="E57" s="111">
         <v>9</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="78">
-        <v>2026</v>
-      </c>
-      <c r="B58" s="79" t="s">
+      <c r="F57" s="79">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="77">
+        <v>2026</v>
+      </c>
+      <c r="B58" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="79" t="s">
+      <c r="C58" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="D58" s="79">
+      <c r="D58" s="78">
         <v>12</v>
       </c>
-      <c r="E58" s="80">
+      <c r="E58" s="111">
         <v>20</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="78">
-        <v>2026</v>
-      </c>
-      <c r="B59" s="79" t="s">
+      <c r="F58" s="79">
+        <f t="shared" si="2"/>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="77">
+        <v>2026</v>
+      </c>
+      <c r="B59" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="79" t="s">
+      <c r="C59" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="79">
+      <c r="D59" s="78">
         <v>4</v>
       </c>
-      <c r="E59" s="80">
+      <c r="E59" s="111">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="78">
-        <v>2026</v>
-      </c>
-      <c r="B60" s="79" t="s">
+      <c r="F59" s="79">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="77">
+        <v>2026</v>
+      </c>
+      <c r="B60" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="79" t="s">
+      <c r="C60" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="79">
+      <c r="D60" s="78">
         <v>50</v>
       </c>
-      <c r="E60" s="80">
+      <c r="E60" s="111">
         <v>38</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="81">
-        <v>2026</v>
-      </c>
-      <c r="B61" s="79" t="s">
+      <c r="F60" s="79">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="80">
+        <v>2026</v>
+      </c>
+      <c r="B61" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="C61" s="82" t="s">
+      <c r="C61" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="82">
+      <c r="D61" s="81">
         <v>25</v>
       </c>
-      <c r="E61" s="83">
+      <c r="E61" s="112">
         <v>12</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="F61" s="82">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>2026</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="84" t="s">
+      <c r="C62" s="83" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="7">
-        <f t="shared" ref="D62:E68" si="0">SUM(D54,D46,D38,D30,D22,D12,D2)</f>
+        <f t="shared" ref="D62:E68" si="3">SUM(D54,D46,D38,D30,D22,D12,D2)</f>
         <v>675</v>
       </c>
-      <c r="E62" s="8">
-        <f t="shared" si="0"/>
+      <c r="E62" s="83">
+        <f t="shared" si="3"/>
         <v>368</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62" s="8">
+        <f t="shared" si="2"/>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>2026</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C63" s="85" t="s">
+      <c r="C63" s="84" t="s">
         <v>20</v>
       </c>
       <c r="D63" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>652</v>
       </c>
-      <c r="E63" s="11">
-        <f t="shared" si="0"/>
+      <c r="E63" s="84">
+        <f t="shared" si="3"/>
         <v>583</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63" s="11">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>2026</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C64" s="85" t="s">
+      <c r="C64" s="84" t="s">
         <v>21</v>
       </c>
       <c r="D64" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>135</v>
       </c>
-      <c r="E64" s="11">
-        <f t="shared" si="0"/>
+      <c r="E64" s="84">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64" s="11">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>2026</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="85" t="s">
+      <c r="C65" s="84" t="s">
         <v>22</v>
       </c>
       <c r="D65" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>257</v>
       </c>
-      <c r="E65" s="11">
-        <f t="shared" si="0"/>
+      <c r="E65" s="84">
+        <f t="shared" si="3"/>
         <v>76</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65" s="11">
+        <f t="shared" si="2"/>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>2026</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C66" s="85" t="s">
+      <c r="C66" s="84" t="s">
         <v>6</v>
       </c>
       <c r="D66" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>134</v>
       </c>
-      <c r="E66" s="11">
-        <f t="shared" si="0"/>
+      <c r="E66" s="84">
+        <f t="shared" si="3"/>
         <v>58</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66" s="11">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>2026</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C67" s="85" t="s">
+      <c r="C67" s="84" t="s">
         <v>23</v>
       </c>
       <c r="D67" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="E67" s="11">
-        <f t="shared" si="0"/>
+      <c r="E67" s="84">
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67" s="11">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>2026</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="85" t="s">
+      <c r="C68" s="84" t="s">
         <v>7</v>
       </c>
       <c r="D68" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>296</v>
       </c>
-      <c r="E68" s="11">
-        <f t="shared" si="0"/>
+      <c r="E68" s="84">
+        <f t="shared" si="3"/>
         <v>247</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F68" s="11">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="12">
         <v>2026</v>
       </c>
       <c r="B69" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C69" s="86" t="s">
+      <c r="C69" s="85" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="13">
         <f>SUM(D61,D53,D45,D37,D29,D21,D11)</f>
         <v>145</v>
       </c>
-      <c r="E69" s="14">
+      <c r="E69" s="85">
         <f>SUM(E61,E53,E45,E37,E29,E21,E11)</f>
         <v>61</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="20">
+      <c r="F69" s="14">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="19">
         <v>2027</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -2043,10 +2343,10 @@
         <v>19</v>
       </c>
       <c r="D70" s="2"/>
-      <c r="E70" s="21"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="18">
+      <c r="E70" s="20"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="17">
         <v>2027</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -2058,8 +2358,8 @@
       <c r="D71" s="1"/>
       <c r="E71" s="4"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="18">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="17">
         <v>2027</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -2071,8 +2371,8 @@
       <c r="D72" s="1"/>
       <c r="E72" s="4"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="18">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="17">
         <v>2027</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -2084,8 +2384,8 @@
       <c r="D73" s="1"/>
       <c r="E73" s="4"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="18">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="17">
         <v>2027</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -2097,8 +2397,8 @@
       <c r="D74" s="1"/>
       <c r="E74" s="4"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="18">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="17">
         <v>2027</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -2110,8 +2410,8 @@
       <c r="D75" s="1"/>
       <c r="E75" s="4"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="18">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="17">
         <v>2027</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -2123,8 +2423,8 @@
       <c r="D76" s="1"/>
       <c r="E76" s="4"/>
     </row>
-    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="19">
+    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="18">
         <v>2027</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -2136,8 +2436,8 @@
       <c r="D77" s="3"/>
       <c r="E77" s="5"/>
     </row>
-    <row r="78" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="20">
+    <row r="78" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="19">
         <v>2027</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -2147,10 +2447,10 @@
         <v>19</v>
       </c>
       <c r="D78" s="2"/>
-      <c r="E78" s="21"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="18">
+      <c r="E78" s="20"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="17">
         <v>2027</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -2162,8 +2462,8 @@
       <c r="D79" s="1"/>
       <c r="E79" s="4"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="18">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="17">
         <v>2027</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -2176,7 +2476,7 @@
       <c r="E80" s="4"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="18">
+      <c r="A81" s="17">
         <v>2027</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -2189,7 +2489,7 @@
       <c r="E81" s="4"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="18">
+      <c r="A82" s="17">
         <v>2027</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -2202,7 +2502,7 @@
       <c r="E82" s="4"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="18">
+      <c r="A83" s="17">
         <v>2027</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -2215,7 +2515,7 @@
       <c r="E83" s="4"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="18">
+      <c r="A84" s="17">
         <v>2027</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -2228,7 +2528,7 @@
       <c r="E84" s="4"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="19">
+      <c r="A85" s="18">
         <v>2027</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -2241,7 +2541,7 @@
       <c r="E85" s="5"/>
     </row>
     <row r="86" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="20">
+      <c r="A86" s="19">
         <v>2027</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -2251,10 +2551,10 @@
         <v>19</v>
       </c>
       <c r="D86" s="2"/>
-      <c r="E86" s="21"/>
+      <c r="E86" s="20"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="18">
+      <c r="A87" s="17">
         <v>2027</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -2267,7 +2567,7 @@
       <c r="E87" s="4"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="18">
+      <c r="A88" s="17">
         <v>2027</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -2280,7 +2580,7 @@
       <c r="E88" s="4"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="18">
+      <c r="A89" s="17">
         <v>2027</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -2293,7 +2593,7 @@
       <c r="E89" s="4"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="18">
+      <c r="A90" s="17">
         <v>2027</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -2306,7 +2606,7 @@
       <c r="E90" s="4"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="18">
+      <c r="A91" s="17">
         <v>2027</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -2319,7 +2619,7 @@
       <c r="E91" s="4"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="18">
+      <c r="A92" s="17">
         <v>2027</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -2332,7 +2632,7 @@
       <c r="E92" s="4"/>
     </row>
     <row r="93" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="19">
+      <c r="A93" s="18">
         <v>2027</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -2345,7 +2645,7 @@
       <c r="E93" s="5"/>
     </row>
     <row r="94" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="20">
+      <c r="A94" s="19">
         <v>2027</v>
       </c>
       <c r="B94" s="2" t="s">
@@ -2355,10 +2655,10 @@
         <v>19</v>
       </c>
       <c r="D94" s="2"/>
-      <c r="E94" s="21"/>
+      <c r="E94" s="20"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="18">
+      <c r="A95" s="17">
         <v>2027</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -2371,7 +2671,7 @@
       <c r="E95" s="4"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="18">
+      <c r="A96" s="17">
         <v>2027</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -2384,7 +2684,7 @@
       <c r="E96" s="4"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="18">
+      <c r="A97" s="17">
         <v>2027</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -2397,7 +2697,7 @@
       <c r="E97" s="4"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="18">
+      <c r="A98" s="17">
         <v>2027</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -2410,7 +2710,7 @@
       <c r="E98" s="4"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="18">
+      <c r="A99" s="17">
         <v>2027</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -2423,7 +2723,7 @@
       <c r="E99" s="4"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="18">
+      <c r="A100" s="17">
         <v>2027</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -2436,7 +2736,7 @@
       <c r="E100" s="4"/>
     </row>
     <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="19">
+      <c r="A101" s="18">
         <v>2027</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -2449,7 +2749,7 @@
       <c r="E101" s="5"/>
     </row>
     <row r="102" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="20">
+      <c r="A102" s="19">
         <v>2027</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -2461,10 +2761,10 @@
       <c r="D102" s="2">
         <v>150</v>
       </c>
-      <c r="E102" s="21"/>
+      <c r="E102" s="20"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="18">
+      <c r="A103" s="17">
         <v>2027</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -2479,7 +2779,7 @@
       <c r="E103" s="4"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="18">
+      <c r="A104" s="17">
         <v>2027</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -2494,7 +2794,7 @@
       <c r="E104" s="4"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="18">
+      <c r="A105" s="17">
         <v>2027</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -2509,7 +2809,7 @@
       <c r="E105" s="4"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="18">
+      <c r="A106" s="17">
         <v>2027</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -2524,7 +2824,7 @@
       <c r="E106" s="4"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="18">
+      <c r="A107" s="17">
         <v>2027</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -2539,7 +2839,7 @@
       <c r="E107" s="4"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="18">
+      <c r="A108" s="17">
         <v>2027</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -2554,7 +2854,7 @@
       <c r="E108" s="4"/>
     </row>
     <row r="109" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="19">
+      <c r="A109" s="18">
         <v>2027</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -2569,7 +2869,7 @@
       <c r="E109" s="5"/>
     </row>
     <row r="110" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="20">
+      <c r="A110" s="19">
         <v>2027</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -2579,10 +2879,10 @@
         <v>19</v>
       </c>
       <c r="D110" s="2"/>
-      <c r="E110" s="21"/>
+      <c r="E110" s="20"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="18">
+      <c r="A111" s="17">
         <v>2027</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -2595,7 +2895,7 @@
       <c r="E111" s="4"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="18">
+      <c r="A112" s="17">
         <v>2027</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -2608,7 +2908,7 @@
       <c r="E112" s="4"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="18">
+      <c r="A113" s="17">
         <v>2027</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -2621,7 +2921,7 @@
       <c r="E113" s="4"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="18">
+      <c r="A114" s="17">
         <v>2027</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -2634,7 +2934,7 @@
       <c r="E114" s="4"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="18">
+      <c r="A115" s="17">
         <v>2027</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -2647,7 +2947,7 @@
       <c r="E115" s="4"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="18">
+      <c r="A116" s="17">
         <v>2027</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -2660,7 +2960,7 @@
       <c r="E116" s="4"/>
     </row>
     <row r="117" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="19">
+      <c r="A117" s="18">
         <v>2027</v>
       </c>
       <c r="B117" s="3" t="s">
@@ -2673,7 +2973,7 @@
       <c r="E117" s="5"/>
     </row>
     <row r="118" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="20">
+      <c r="A118" s="19">
         <v>2027</v>
       </c>
       <c r="B118" s="2" t="s">
@@ -2683,10 +2983,10 @@
         <v>19</v>
       </c>
       <c r="D118" s="2"/>
-      <c r="E118" s="21"/>
+      <c r="E118" s="20"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="18">
+      <c r="A119" s="17">
         <v>2027</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -2699,7 +2999,7 @@
       <c r="E119" s="4"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="18">
+      <c r="A120" s="17">
         <v>2027</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -2712,7 +3012,7 @@
       <c r="E120" s="4"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="18">
+      <c r="A121" s="17">
         <v>2027</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -2725,7 +3025,7 @@
       <c r="E121" s="4"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="18">
+      <c r="A122" s="17">
         <v>2027</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -2738,7 +3038,7 @@
       <c r="E122" s="4"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="18">
+      <c r="A123" s="17">
         <v>2027</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -2751,7 +3051,7 @@
       <c r="E123" s="4"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="18">
+      <c r="A124" s="17">
         <v>2027</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -2764,7 +3064,7 @@
       <c r="E124" s="4"/>
     </row>
     <row r="125" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="19">
+      <c r="A125" s="18">
         <v>2027</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -2773,11 +3073,11 @@
       <c r="C125" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D125" s="22"/>
-      <c r="E125" s="23"/>
+      <c r="D125" s="21"/>
+      <c r="E125" s="22"/>
     </row>
     <row r="126" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="20">
+      <c r="A126" s="19">
         <v>2027</v>
       </c>
       <c r="B126" s="2" t="s">
@@ -2787,16 +3087,16 @@
         <v>19</v>
       </c>
       <c r="D126" s="2">
-        <f t="shared" ref="D126:E126" si="1">SUM(D118,D110,D102,D94,D86,D78,D70)</f>
+        <f t="shared" ref="D126:E126" si="4">SUM(D118,D110,D102,D94,D86,D78,D70)</f>
         <v>150</v>
       </c>
-      <c r="E126" s="21">
-        <f t="shared" si="1"/>
+      <c r="E126" s="20">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="18">
+      <c r="A127" s="17">
         <v>2027</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -2806,16 +3106,16 @@
         <v>20</v>
       </c>
       <c r="D127" s="1">
-        <f t="shared" ref="D127:E127" si="2">SUM(D119,D111,D103,D95,D87,D79,D71)</f>
+        <f t="shared" ref="D127:E127" si="5">SUM(D119,D111,D103,D95,D87,D79,D71)</f>
         <v>160</v>
       </c>
       <c r="E127" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="18">
+      <c r="A128" s="17">
         <v>2027</v>
       </c>
       <c r="B128" s="1" t="s">
@@ -2825,16 +3125,16 @@
         <v>21</v>
       </c>
       <c r="D128" s="1">
-        <f t="shared" ref="D128:E128" si="3">SUM(D120,D112,D104,D96,D88,D80,D72)</f>
+        <f t="shared" ref="D128:E128" si="6">SUM(D120,D112,D104,D96,D88,D80,D72)</f>
         <v>40</v>
       </c>
       <c r="E128" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="18">
+      <c r="A129" s="17">
         <v>2027</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -2844,16 +3144,16 @@
         <v>22</v>
       </c>
       <c r="D129" s="1">
-        <f t="shared" ref="D129:E129" si="4">SUM(D121,D113,D105,D97,D89,D81,D73)</f>
+        <f t="shared" ref="D129:E129" si="7">SUM(D121,D113,D105,D97,D89,D81,D73)</f>
         <v>35</v>
       </c>
       <c r="E129" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="18">
+      <c r="A130" s="17">
         <v>2027</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -2863,16 +3163,16 @@
         <v>6</v>
       </c>
       <c r="D130" s="1">
-        <f t="shared" ref="D130:E130" si="5">SUM(D122,D114,D106,D98,D90,D82,D74)</f>
+        <f t="shared" ref="D130:E130" si="8">SUM(D122,D114,D106,D98,D90,D82,D74)</f>
         <v>25</v>
       </c>
       <c r="E130" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="18">
+      <c r="A131" s="17">
         <v>2027</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -2882,16 +3182,16 @@
         <v>23</v>
       </c>
       <c r="D131" s="1">
-        <f t="shared" ref="D131:E131" si="6">SUM(D123,D115,D107,D99,D91,D83,D75)</f>
+        <f t="shared" ref="D131:E131" si="9">SUM(D123,D115,D107,D99,D91,D83,D75)</f>
         <v>3</v>
       </c>
       <c r="E131" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="18">
+      <c r="A132" s="17">
         <v>2027</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -2901,16 +3201,16 @@
         <v>7</v>
       </c>
       <c r="D132" s="1">
-        <f t="shared" ref="D132:E132" si="7">SUM(D124,D116,D108,D100,D92,D84,D76)</f>
+        <f t="shared" ref="D132:E132" si="10">SUM(D124,D116,D108,D100,D92,D84,D76)</f>
         <v>60</v>
       </c>
       <c r="E132" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="19">
+      <c r="A133" s="18">
         <v>2027</v>
       </c>
       <c r="B133" s="3" t="s">
